--- a/自考本科/个人学习笔记/Byvm815/毕业时间预测表.xlsx
+++ b/自考本科/个人学习笔记/Byvm815/毕业时间预测表.xlsx
@@ -62,8 +62,31 @@
 达到毕业要求</t>
   </si>
   <si>
-    <t xml:space="preserve">最晚自考本科申请毕业时间
-（如果考研）</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t>最晚自考本科申请毕业时间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t>（如果考研）</t>
+    </r>
   </si>
   <si>
     <t>七月</t>
@@ -90,8 +113,23 @@
     <t>自考本科笔试补考机会</t>
   </si>
   <si>
-    <t xml:space="preserve">国开专科毕业信息录入学信网
-（可以报名考研了）</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t xml:space="preserve">国开专科毕业信息录入学信网
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t>（可以报名考研了）</t>
+    </r>
   </si>
   <si>
     <t>十一月</t>
@@ -104,15 +142,30 @@
 （需要笔试实践全部通过）</t>
   </si>
   <si>
-    <t xml:space="preserve">自考本科申请毕业
-（可以参加研究生考试了）</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t xml:space="preserve">自考本科申请毕业
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="等距更纱黑体 SC Light"/>
+      </rPr>
+      <t>（可以参加研究生考试了）</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -128,6 +181,11 @@
       <b/>
       <sz val="11.000000"/>
       <color theme="1"/>
+      <name val="等距更纱黑体 SC Light"/>
+    </font>
+    <font>
+      <sz val="8.000000"/>
+      <color theme="0" tint="-0.499984740745262"/>
       <name val="等距更纱黑体 SC Light"/>
     </font>
   </fonts>
@@ -219,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
     <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -244,6 +302,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="1" fillId="0" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -765,8 +826,7 @@
     <col customWidth="1" min="9" max="9" style="1" width="1.7109375"/>
     <col min="10" max="10" style="1" width="9.140625"/>
     <col customWidth="1" min="11" max="11" style="1" width="28.7109375"/>
-    <col min="12" max="12" style="1" width="9.140625"/>
-    <col min="13" max="16384" style="1" width="9.140625"/>
+    <col min="12" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75">
@@ -991,7 +1051,7 @@
       <c r="J10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="10" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1042,29 +1102,29 @@
       <c r="K12" s="6"/>
     </row>
     <row r="13" ht="40.100000000000001" customHeight="1">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="11"/>
+      <c r="B13" s="12"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="13" t="s">
         <v>26</v>
       </c>
       <c r="F13" s="7"/>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="13" t="s">
         <v>27</v>
       </c>
       <c r="I13" s="9"/>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="K13" s="11"/>
+      <c r="K13" s="12"/>
     </row>
     <row r="14" ht="14.25">
       <c r="D14" s="1"/>

--- a/自考本科/个人学习笔记/Byvm815/毕业时间预测表.xlsx
+++ b/自考本科/个人学习笔记/Byvm815/毕业时间预测表.xlsx
@@ -64,7 +64,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="8"/>
         <color theme="0" tint="-0.499984740745262"/>
         <rFont val="等距更纱黑体 SC Light"/>
       </rPr>
@@ -157,7 +157,8 @@
         <color theme="0" tint="-0.499984740745262"/>
         <rFont val="等距更纱黑体 SC Light"/>
       </rPr>
-      <t>（可以参加研究生考试了）</t>
+      <t xml:space="preserve">（可以参加研究生考试了）
+最晚自考本科报考毕业论文时间</t>
     </r>
   </si>
 </sst>
